--- a/resources/data/BANCOCNPJ.xlsx
+++ b/resources/data/BANCOCNPJ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1968"/>
+  <dimension ref="A1:B2169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20091,10 +20091,8 @@
       </c>
     </row>
     <row r="1967">
-      <c r="A1967" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   38239657869</t>
-        </is>
+      <c r="A1967" t="n">
+        <v>38239657869</v>
       </c>
       <c r="B1967" t="inlineStr">
         <is>
@@ -20103,14 +20101,2300 @@
       </c>
     </row>
     <row r="1968">
-      <c r="A1968" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   00840815034</t>
-        </is>
+      <c r="A1968" t="n">
+        <v>840815034</v>
       </c>
       <c r="B1968" t="inlineStr">
         <is>
           <t>NAO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="n">
+        <v>24107697000162</v>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAIZ COMERCIO DE ALIMENTOS LTDA                      </t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="n">
+        <v>13557765000179</v>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RM INDUSTRIA E MONTAGEM DE MOVEIS L                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="n">
+        <v>5582038000133</v>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIRAPURU INDUSTRIA E COMERCIO DE AG                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="n">
+        <v>7272825000457</v>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNO INDUSTRIA E COMERCIO DE COMPU                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="n">
+        <v>7749764000204</v>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIVINA PICANHA COMERCIO DE ALIMENTO                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="n">
+        <v>13073679000190</v>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S VIEIRA DA SILVA                                    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="n">
+        <v>212872000113</v>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASA SUL INDUSTRIA E COMERCIO DE MAL                  </t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="n">
+        <v>43283811015262</v>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KALUNGA SA                                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="n">
+        <v>9113843000683</v>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMERCIAL BRASIL DISTRIBUIDORA DE E                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="n">
+        <v>5483270000114</v>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMERCIAL DE PETROLEO PARAIBANO LTD                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="n">
+        <v>68422419000760</v>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PALACIO DAS FERRAMENTAS E PARAFUSOS              </t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="n">
+        <v>47960950090449</v>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAGAZINE LUIZA S/A                                   </t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="n">
+        <v>43910557000172</v>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KONFEKT LTDA                                                  </t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="n">
+        <v>34681828000174</v>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTO POSTO REZENDE LTDA                             </t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="n">
+        <v>49848136000145</v>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BARBARA MAFRA ROMERO ONO                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="n">
+        <v>34740577000151</v>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ MARTINS - DM CELULAR                                       </t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="n">
+        <v>1157555006307</v>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENDA ATACADO SA                                              </t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="n">
+        <v>61052607000100</v>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> NOEL VAGNER DE MEIRA                               </t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="n">
+        <v>83044016008450</v>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARA COMERCIO DE ALIMENTOS LTDA                              </t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="n">
+        <v>46814281000117</v>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTO POSTO JASMIM LIMITADA                                    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="n">
+        <v>8165676000147</v>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J CENTRO BAR E RESTAURANTE LTDA                              </t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="n">
+        <v>83483230000186</v>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SELBETTI TECNOLOGIA SA                             </t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="n">
+        <v>41905509000160</v>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUNDO MULTI SHOP COMERCIO DIGITAL L                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="n">
+        <v>60445665000130</v>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PANIFICADORA CECI LTDA                            </t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="n">
+        <v>42953030000162</v>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESTAURANTE MARGINAL TIETE LTDA                               </t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="n">
+        <v>11055823000130</v>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUFFET E REFEICOES ANHEMBI LTDA                               </t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="n">
+        <v>66716002305</v>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOGIN INFORMATICA COMERCIO E REPRES                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="n">
+        <v>8927259000194</v>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALU DISTRIBUIDORA DE EPI E MRO LTD                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="n">
+        <v>69320505000130</v>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORIZETTI SERVICOS DE ALIMENTACAO L               </t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="n">
+        <v>18966590000177</v>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RB NOTE ASSISTENCIA TECNICA LTDA                              </t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="n">
+        <v>27229847000107</v>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KM FIX COMERCIO DE FIXADORES ORGANI                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="n">
+        <v>40654486000104</v>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRAL DOS SALGADOS COMERCIO DE AL                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="n">
+        <v>8584116000984</v>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WEBCONTINENTAL LTDA                                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="n">
+        <v>44600832000114</v>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DK SHOWS E PROMOCAO DE VENDAS LTDA                            </t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="n">
+        <v>18097069000140</v>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTO POSTO ZANI BADY BASSITT LTDA                 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="n">
+        <v>60963215000130</v>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DANILO VASQUES FERRES                                         </t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="n">
+        <v>9325695000237</v>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTISTA COMERCIAL DE EMBALAGEM LTD                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="n">
+        <v>13010430000136</v>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOSSA FLORA COMERCIO DE PLANTAS E F                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="n">
+        <v>46384400008476</v>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECRETARIA DE AGRICULTURA E ABASTEC                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="n">
+        <v>47020113000112</v>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR NASCIMENTO LTDA                                            </t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="n">
+        <v>28615629000165</v>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELABI COMERCIO DE VARIEDADE LTDA                             </t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="n">
+        <v>22645564000114</v>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALESSANDRA VITORINO FERREIRA                      </t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="n">
+        <v>43967691000100</v>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DECAZZA COMERCIAL LTDA                                       </t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="n">
+        <v>14244294000101</v>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAX FERRAMENTAS LTDA                             </t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="n">
+        <v>48076228001910</v>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMARINHOS FERNANDO LTDA                          </t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="n">
+        <v>18983263000123</v>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AFC COMERCIO VAREJISTA DE COMPONENT                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="n">
+        <v>6031381000152</v>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIS PROVEDOR SERVICOS DE INTERNET                </t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="n">
+        <v>3639749000171</v>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSPERAL EMBALAGENS                                          </t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="n">
+        <v>43288178000192</v>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISTRIBUIDORA PONTO DA BEBIDA LTDA                            </t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="n">
+        <v>22581135000120</v>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SORVETES MAUA LTDA                                            </t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="n">
+        <v>1438784003899</v>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEROY MERLIN CIA BRASILEIRA DE BRIC               </t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="n">
+        <v>61257900000103</v>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> NUBIA SOARES SILVA                                 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="n">
+        <v>52985077000161</v>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELICIA SABOR DE CHOCOLATE LTDA                               </t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="n">
+        <v>3746938001620</v>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRS SUPRIMENTOS CORPORATIVOS S/A                  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="n">
+        <v>18939564000150</v>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOJA TORRES UTENSILIOS DOMESTICOS L                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="n">
+        <v>5608845000188</v>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTO POSTO POLI JARAGUA LTDA                      </t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="n">
+        <v>32054796000151</v>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JJ DE VASCONCELOS COMERCIO E DISTR                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="n">
+        <v>45616496000160</v>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B3UP COMERCIAL LTDA                                           </t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="n">
+        <v>35242766000167</v>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIO AUGUSTO KAWAMURA                             </t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="n">
+        <v>10524477000120</v>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JR GUSZAKI GAS AGUA E CIA LTDA                               </t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="n">
+        <v>59105101000170</v>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFEICOES BOM APETITT E CIA LTDA                              </t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="n">
+        <v>5483386000153</v>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADRIANO TREVIZAN &amp; CIA LTDA                                  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>62874775000143</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>VIA FORTAL CONSULTORIA DE ENGENHARIA E ARQUITETURA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>62961165000187</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>E. KATRINNE FERREIRA DE CARVALHO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>60274967000193</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>CAFIO ENGENHARIA E CONSULTORIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>62750199000122</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>62.750.199 PEDRO FERREIRA DOS SANTOS NETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>62667138000104</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>SERGIO MENEZES CARDOSO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>60251710000116</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>BRUNO SALES SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>62715097000176</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>ENGSOLUT ENGENHARIA E CONSULTORIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>62972537000170</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>IOB ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>62781338000185</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>H S LIMA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>62709911000140</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>LEONARDO RODRIGUES FEITOSA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>52624925000107</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>B R DA S DE FREITAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>49502183000132</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>GB SERVICOS DE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>55483610000185</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>ANDRE L.M. MARENGO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>51017468000120</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>RMNS SERVICOS DE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>45720219000101</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>ENGIMA ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>44225527000190</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>CARLOS A. C. ERBELLA ENGENHARIA AVALIACOES E PERICIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>06228418000137</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>RVB CONSTRUCOES LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>31509643000199</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>T R H ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>41907259000106</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>VENICIO EDUARDO ELOI DA SILVA ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>63594591000192</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>MAURO RICARDO ROXO NOBREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>44446618000155</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>A. B. DA CUNHA ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>63332679000136</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>WRK ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>43656728000189</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>KYRO CONSULTORIA EM TECNOLOGIA DA INFORMACAO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>21257726000184</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>L A LIMA DE SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>02874019000192</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>CLIMEG - MEDICINA E SEGURANCA DO TRABALHO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>21568058000297</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>E S LIMA SERVICOS MEDICOS E SAUDE OCUPACIONAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>07287972000158</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>PINACOPY COMERCIO DE PAPELARIA E INFORMATICA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>31009156000167</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>GM CONTABILIDADE LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>58512721000160</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>ANA PATRICIA PSICOLOGIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>61054015000127</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>WAGNER OLIVEIRA DE PAULA SERVICOS DE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>61789294000177</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>DELTA TI SOLUCOES EMPRESARIAIS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>61762262000188</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>OCURI LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>30027324000184</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>J CASCIMIRO DE OLIVEIRA ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>05704907000155</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>EDSON HIROYUKI UJIKAWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>18881665000117</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>RACANICCHI CONSULTORIA E PROJETOS DE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>18351923000153</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>TR AMBIENTAL CONSULTORIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>32142545000129</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>DOLCE ARQUITETURA E CONSULTORIA AMBIENTAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>33773305000195</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>JESSICA R DE MELLO SERVICOS DE ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>46230018000180</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>OTTON DE SOUZA BARBOSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>60969721000136</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>LINDOJF SERVICOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>51556929000132</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>JDR BIM ARCHITECTURE AND CONSULTANCY LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>55058500000176</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>ATEX SOLUCOES INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>23156469000110</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>BRUNO DANIEL ORTIS GIMENES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>55009160000193</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>MMS SEGURANCA E SAUDE OCUPACIONAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>59250954000103</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>AMANDA LOPES DE ARAUJO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>60951748000100</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>KURAHARA ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>61166456000110</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>OLMA ENGENHARIA CIVIL E SEGURANCA DO TRABALHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>60400237000191</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>ANDRE GOMES MENDONCA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>40203384000164</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>LFA CONSULTORIA EDUCACIONAL E GESTAO DE PESSOAS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>57011738000171</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>CERTUS ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>47439082000139</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>NSG-MARKETING,PUBLICIDADE &amp; PROMOCOES LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>51707264000110</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>SOLUTION DESENTUPIDORA SERVICOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>23412247000110</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>AMAZON AWS SERVICOS BRASIL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>41817022000126</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>ERIC ANIZ CONSULTORIA E GERENCIAMENTO DE OBRAS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>07763076000118</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>HOTEL PRAIAS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>22707399000188</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>PELEGRINA &amp; BRANDAO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>62473642000165</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>LIGYA RODRIGUES ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>49441848000145</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>DIEGO SIQUEIRA DE OLIVEIRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>31338913000146</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>THIAGO FAVARON MANTOVANI 28878924873</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>62794179000153</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>GABRIEL JOAQUIM GONCALVES MARTINAZZO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>47735780000181</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>LEONARDO DA SILVA BEVILACQUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>50051513000108</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>50.051.513 GABRIEL BORGO DE MIRANDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>48693124000126</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>SASSA SERVICO DE CONSULTORIA EM ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>37565063000103</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>FELIPE AMERICO DE SOUZA 32350529843</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>63622212000120</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>BRUNA DA SILVA ANTUNES LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>62529994000195</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>ETKENGE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>60588681000182</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>TECNOPLAN GESTAO EMPRESARIAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>44042258000126</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>TRIANGULAIRE CONSULTORIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>27909911000192</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>IDEAL PEOPLE LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>47603767000179</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>47.603.767 LUIZ TEIXEIRA MENDES DE CARVALHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>61019648000102</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>PEVEC SERVICOS ADMINISTRATIVOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>07091641000148</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>G3 SEGURANCA PRIVADA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>00910767005460</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>REGUS DO BRASIL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>63832813000168</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>ELLEN FLORES DE OLIVEIRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>60623698000123</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>JACKELINE OLIVEIRA SANTOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>13532814000119</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>INPARK ADMINISTRACAO DE ESTACIONAMENTOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>62004907000186</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>MALI ASSESSORIA E CONSULTORIA EMPRESARIAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>62737604000172</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>NAVAS &amp;CVIAS SERVICOS DE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>62868171000194</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>CARUSO ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>10969563000146</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>G.M. SERVICOS DE EVENTOS E ESCRITORIOS COMPARTILHADOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>17667187000184</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>AELSKE ARQUITETURA S/S LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>60620782000193</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>MAG BIM ELECTRICAL PROJECTS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>22998543000182</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>G70 PARK LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>62605020000143</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>62.605.020 MATHEUS SANTOS MELO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>65083925000199</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>A36 PROJETOS INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>06223867000192</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>MJS CONSULTORIA E ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>61086600000109</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>C.M SERVICOS DE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>44903894000103</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>PHS ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>13253825000160</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>P V D MAIA PROJETOS DE ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>63711087000125</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>MARCIO ARRUDA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>53609224000161</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>VH CONSTRUCAO DE EDIFICIOS E SERVICOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>50450917000166</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>RGAMOSA ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>12584668000102</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>PERSA CONSTRUTORA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>38061531000167</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>ARIANY LEAO SILVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>07532389000165</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>ARAL ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>63562754000155</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>DJALMA DONATO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>46330065000104</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>MARCELO PESSINI POMPEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>54324484000153</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>RODAN SERVICOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>62471471000135</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>DESK TEC SOLUCOES ADMINISTRATIVAS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>28240211000110</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>BSINE IMPRESSOS PERSONALIZADOS E COMERCIO LTDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>07887077000174</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>CELSO JOSE FLORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>61462840000160</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>TFP PRIME ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>48019091000133</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>LUCAS DE ASSIS LEMES ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>57451907000194</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>MANTUA ENGENHARIA E PROJETOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>60415910000167</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>FERNANDA NASCIMENTO NERY DIAS CONSULTORIA AMBIENTAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>58455089000160</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>KDT ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>51148653000153</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>LOURENCO CONSULTORIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>17594619000174</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>J M BORDINHON OBRAS DE ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>86765500000130</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>SP LASER COPIAS ESPECIAIS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>74232067000198</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>CASA D'ANGELO MATERIAIS PARA CONSTRUCAO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>54817083000135</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>54.817.083 KAUA DA MOTTA PINTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>07933858000158</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>POLAR RIO HOTEL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>07182046000118</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>HOTEL DAN INN SAO JOSE LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>44965233000102</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>R A L PARK ESTACIONAMENTO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>32133157000181</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>WALQUIRIA DOS SANTOS SILVA 25987544840</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>40939689000139</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>CENTERB RP LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>57036306000115</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>MMPG SERVICOS E PARTICIPACOES LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>63222552000164</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>KMM PROJETOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>61642416000106</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>SK ARQUEOLOGIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>61836098000106</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>PINDO - HISTORIA, ARQUEOLOGIA E PATRIMONIO CULTURAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>60123343000175</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>VHL ENGENHARIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>42261992000150</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>HV CONSULTORIA EM ARQUEOLOGIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>15344871000108</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>ABA ALBUQUERQUE BISCAIA ENGENHARIA DE ESTRUTURAS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>03563927000128</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>ATRIUM CONSULTORIA E PROJETOS S/C LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>33991526000130</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>NICOLAS DA SILVA TIBURCIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>62627124000159</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>IGOR PELEGRINELI DIAS ARQUITETURA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>60498426000149</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>FLC TEIXEIRA SERVICOS ADMINISTRATIVOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>62182374000122</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>62.182.374 MARCOS KENGO MASUDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>62438041000111</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>NICOLAS MIRANDA ARQUITETURA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>61521214000106</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>61.521.214 VITORIA DE LIMA SOARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>52212486000125</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>OCAETE GESTAO SOCIAL E SERVICOS ADMINISTRATIVOS LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>60700255000199</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>60.700.255 LILIAN NAPOLITANO ESTANISLAU SAMPAIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>63260265000149</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>63.260.265 MATHEUS SAMPAIO TAVARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>33333710000192</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>FIRELUZ COMERCIO E MANUTENCAO DE MATERIAIS CONTRA INCENDIO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>40763254000186</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>I35 PROTECAO E INTEGRACAO SOCIAL LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>29302933000115</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>UNITY SERVICOS DE IMPRESSAO LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>63019714000161</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>CAROLINA PASSOS SILVA CONSULTORIA LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>60476323000188</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>NANE DESIGNER LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>60720025000191</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>60.720.025 VALERIA CALIXTO DE ALMEIDA SANTOS</t>
         </is>
       </c>
     </row>
